--- a/AI Audit Log_VoThiHongNgoc.xlsx
+++ b/AI Audit Log_VoThiHongNgoc.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vongoc/Desktop/swd/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vongoc/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3EB10E1-5EA3-654C-858C-E73018F40B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{27D5328A-C92B-C74A-820A-88B12C0A302A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="2" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
-    <sheet name="Assignment 1" sheetId="2" r:id="rId2"/>
-    <sheet name="Assignment 2" sheetId="3" r:id="rId3"/>
+    <sheet name="Chap6" sheetId="2" r:id="rId2"/>
+    <sheet name="Chap7" sheetId="3" r:id="rId3"/>
     <sheet name="Assignment 3" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="48">
   <si>
     <t>Ví dụ: Abstraction</t>
   </si>
@@ -254,6 +254,414 @@
 - Về mặt tư duy phân tích: Nhờ ví dụ cây ATM, tôi đã phân biệt rạch ròi được: Include là sự phụ thuộc "sống còn" (Dependency), còn Extend chỉ là tính năng "có thì tốt, không có vẫn xong" (Optional/Alternative).
 - Về mặt kỹ thuật vẽ biểu đồ (UML): Nhận ra lỗi sai sơ đẳng sinh viên hay mắc phải là vẽ sai chiều mũi tên của Extend. Từ nay, tôi khắc cốt ghi tâm quy tắc: Include thì mũi tên đi tiến (chỉ vào thằng bị phụ thuộc), Extend thì mũi tên đi lùi (chỉ ngược về thằng gốc).
 - Dưới góc nhìn kiểm thử phần mềm (QA/Testing): Khi viết test case, với luồng &lt;&lt;include&gt;&gt; tôi phải luôn đưa vào kịch bản kiểm thử chính (Happy Path). Nhưng với luồng &lt;&lt;extend&gt;&gt;, tôi phải tạo các kịch bản rẽ nhánh (Alternative/Exception) để kiểm tra xem điều kiện kích hoạt (ví dụ: bấm nút "Yes" in biên lai) có hoạt động đúng hay không.</t>
+    </r>
+  </si>
+  <si>
+    <t>Khái niệm &amp; Mục đích của Static Model</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Phản hồi của AI: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve">AI giải thích Static Modeling giải quyết góc nhìn cấu trúc tĩnh của một bài toán, góc nhìn này không thay đổi theo thời gian. Nó định nghĩa các lớp (classes), thuộc tính (attributes), mối quan hệ (relationships) và các phương thức (operations) trong hệ thống. Cấu trúc tĩnh của hệ thống được cho là ít có khả năng thay đổi hơn so với các chức năng của hệ thống. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve">
+Quyết định của người học (Reflection): </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>Nắm được bản chất nền tảng của mô hình tĩnh. Rút kinh nghiệm: Khi thiết kế hệ thống, tôi sẽ ưu tiên việc xác định và đóng băng cấu trúc các lớp (Class) và mối quan hệ trước, vì đây là bộ khung vững chắc nhất để xây dựng các chức năng động thay đổi theo thời gian sau này.</t>
+    </r>
+  </si>
+  <si>
+    <t>Đối tượng (Object), Lớp (Class) &amp; Thuộc tính</t>
+  </si>
+  <si>
+    <t>Phân biệt sự khác nhau giữa Object và Class. Lấy ví dụ minh họa về các thuộc tính (Attribute) và chức năng (Functionality) của một Lớp.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Phản hồi của AI: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AI định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Một Đối tượng (Object) là một "sự vật" đơn lẻ (ví dụ: một tài khoản cụ thể, một nhân viên cụ thể). Một Lớp (Class) là tập hợp các đối tượng có chung đặc điểm (ví dụ: lớp tài khoản, lớp nhân viên). Thuộc tính là giá trị dữ liệu được giữ bởi các đối tượng (như Name, Age, Account Number). Chức năng là các hành vi như Walk(), Eat(), Work().  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Quyết định của người học (Reflection): </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Phân biệt rõ ràng giữa mẫu chung (Class) và phiên bản cụ thể (Object). Quyết định: Trong biểu đồ Class Diagram, tôi chỉ mô hình hóa các Class trừu tượng mang tính đại diện chung, đồng thời xác định danh sách các Attribute cần thiết để lưu trữ dữ liệu cho từng đối tượng sau này.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mô hình hóa Mối quan hệ Hiệp hội (Association)</t>
+  </si>
+  <si>
+    <t>Giải thích cách mô tả mối quan hệ Association giữa các lớp và ý nghĩa của các thông số đa dạng (Multiplicity) như 1, 0..1, , 1…</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Phản hồi của AI: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">AI chỉ ra Association định nghĩa mối quan hệ cấu trúc tĩnh giữa các lớp, thường được biểu diễn bằng động từ hoặc cụm động từ (ví dụ: Employee Works in Department). Các giá trị bản số bao gồm: 1 (Chính xác một), 0..1 (Tùy chọn - không hoặc một), * (Nhiều - không hoặc nhiều), 1..* (Nhiều - một hoặc nhiều). 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Quyết định của người học (Reflection): </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hiểu rõ tầm quan trọng của việc gán bản số (multiplicity) trong sơ đồ lớp. Rút kinh nghiệm: Khi nối 2 class, tôi luôn phải đặt câu hỏi hai chiều (ví dụ: "1 Khách hàng có thể có bao nhiêu Thẻ?", "1 Thẻ thuộc về bao nhiêu Khách hàng?") để điền chính xác bản số, đảm bảo tính đúng đắn cho</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cơ sở dữ liệu sau này.</t>
+    </r>
+  </si>
+  <si>
+    <t>Phân biệt Composition &amp; Aggregation</t>
+  </si>
+  <si>
+    <t>Sự khác nhau giữa Composition và Aggregation trong mối quan hệ Whole/Part (Toàn thể/Bộ phận) là gì?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Phản hồi của AI:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI tóm tắt cả hai đều giải quyết cấu trúc một lớp được tạo thành từ các lớp khác. Tuy nhiên, Composition là mối quan hệ mà các đối tượng bộ phận được tạo ra, tồn tại và chết đi cùng với toàn thể. Aggregation là dạng yếu hơn, các phần tử bộ phận có thể được thêm vào hoặc loại bỏ khỏi khối tổng thể. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định của người học (Reflection):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Nhận diện được mức độ phụ thuộc "sống còn" giữa các đối tượng. Quyết định: Tôi sẽ dùng hình thoi đen (Composition) cho các thành phần không thể tồn tại độc lập (như ATM và Khe đọc thẻ), và hình thoi trắng (Aggregation) cho các thành phần có thể tồn tại rời (như Trường học và Khoa).</t>
+    </r>
+  </si>
+  <si>
+    <t>Context Modeling &amp; Phân loại Stereotypes</t>
+  </si>
+  <si>
+    <t>Trình bày mục đích của Context Modeling và cách sử dụng UML Stereotypes để phân loại lớp.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Phản hồi của AI:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI giải thích Context Modeling giúp xác định rõ cái gì nằm bên trong hệ thống và cái gì nằm bên ngoài. Stereotypes được dùng để phân loại theo vai trò: «entity», «boundary», «control» cho ứng dụng , và «external system» hoặc «external user» cho môi trường bên ngoài.  
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định của người học (Reflection):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Hiểu được cách thiết lập không gian hệ thống. Quyết định: Trước khi vẽ Class Diagram nội bộ, tôi phải vẽ System Context Diagram sử dụng đúng Stereotypes để làm rõ phần mềm tương tác với ai/cái gì bên ngoài.</t>
+    </r>
+  </si>
+  <si>
+    <t>Ternary &amp; Unary Associations</t>
+  </si>
+  <si>
+    <t>Hãy phân biệt và cho ví dụ về Unary association và Ternary association trong thiết kế lớp.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Phản hồi của AI:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI định nghĩa Ternary association là mối quan hệ ba chiều giữa các lớp. Unary association (self-association) là sự liên kết giữa một đối tượng của một lớp với một đối tượng khác trong chính lớp đó  (ví dụ: Person kết hôn với Person) .  
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định của người học (Reflection):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Rút kinh nghiệm: Khi phân tích hệ thống phân cấp (như Employee là sếp của một Employee khác) hoặc một giao dịch có 3 bên tham gia (Buyer, Seller, Agent), tôi sẽ áp dụng quan hệ tự thân hoặc quan hệ ngôi ba để tối ưu mô hình.</t>
+    </r>
+  </si>
+  <si>
+    <t>Association Classes (Lớp liên kết)</t>
+  </si>
+  <si>
+    <t>Generalization / Specialization (Kế thừa)</t>
+  </si>
+  <si>
+    <t>Khi nào thì cần sử dụng Association Class (Lớp liên kết)? Lấy ví dụ minh họa.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Phản hồi của AI:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI hướng dẫn: Association Class là một lớp mô hình hóa mối quan hệ giữa hai hay nhiều lớp. Điều này thường xảy ra nhất trong các mối quan hệ nhiều-nhiều, khi một thuộc tính không thuộc về bất kỳ lớp nào mà thuộc về chính mối quan hệ đó. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Quyết định của người học (Reflection): </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hiểu cách giải quyết các thuộc tính "lơ lửng". Quyết định: Khi thiết kế database sau này, các Association Class (ví dụ: lớp "Hours" cho quan hệ "Works on" giữa Employee và Project) chính là tiền đề để tôi tạo ra các bảng trung gian.</t>
+    </r>
+  </si>
+  <si>
+    <t>Giải thích khái niệm Superclass, Subclass và mối quan hệ "IS A" trong mô hình tĩnh.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Phản hồi của AI:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI định nghĩa: Các thuộc tính chung được trừu tượng hóa thành một lớp khái quát hóa (superclass). Các thuộc tính khác biệt là đặc tính của lớp chuyên biệt hóa (subclass). Có một mối quan hệ "Is a" (LÀ MỘT) giữa subclass và superclass.  
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Quyết định của người học (Reflection): </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cải tiến quy trình thiết kế: Áp dụng Generalization để gom nhóm các thuộc tính chung (như ID, Name, Address) lên lớp cha. Điều này giúp sơ đồ lớp gọn gàng, có tính hệ thống và code không bị lặp lại (áp dụng nguyên tắc DRY - Don't Repeat Yourself).</t>
     </r>
   </si>
 </sst>
@@ -338,7 +746,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -372,6 +780,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -868,9 +1282,144 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A16565-6ACB-4DDB-B0C1-55C7722368A3}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="8.83203125" style="7"/>
+    <col min="2" max="2" width="26.1640625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="28" style="7" customWidth="1"/>
+    <col min="4" max="4" width="56.33203125" style="7" customWidth="1"/>
+    <col min="5" max="16384" width="8.83203125" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="11"/>
+    </row>
+    <row r="2" spans="1:5" ht="176" x14ac:dyDescent="0.2">
+      <c r="A2" s="7">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="176" x14ac:dyDescent="0.2">
+      <c r="A3" s="7">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="176" x14ac:dyDescent="0.2">
+      <c r="A4" s="7">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="176" x14ac:dyDescent="0.2">
+      <c r="A5" s="7">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="144" x14ac:dyDescent="0.2">
+      <c r="A6" s="7">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="144" x14ac:dyDescent="0.2">
+      <c r="A7" s="7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="144" x14ac:dyDescent="0.2">
+      <c r="A8" s="7">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="144" x14ac:dyDescent="0.2">
+      <c r="A9" s="7">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
